--- a/output/resumen_filtrado.xlsx
+++ b/output/resumen_filtrado.xlsx
@@ -513,51 +513,51 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-15, 2026-03-16, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-15, 2026-03-16, 2026-03-24</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2026-03-07, 2026-03-15, 2026-03-21, 2026-03-30</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="n">
         <v>0</v>
       </c>
-      <c r="H2" t="n">
+      <c r="N2" t="n">
         <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2026-03-07, 2026-03-15, 2026-03-21, 2026-03-30</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>2026-03-07, 2026-03-21</t>
-        </is>
-      </c>
-      <c r="M2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.5</v>
       </c>
     </row>
     <row r="3">
@@ -637,12 +637,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>JUEVES</t>
+          <t>MARTES</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -652,23 +652,23 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-10, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>VIERNES</t>
+          <t>MIERCOLES</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -678,14 +678,14 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-06, 2026-03-25</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N4" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
@@ -701,34 +701,38 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2026-03-17, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-03-17, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>MIERCOLES</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2026-03-17, 2026-03-24</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>JUEVES</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">

--- a/output/resumen_filtrado.xlsx
+++ b/output/resumen_filtrado.xlsx
@@ -523,19 +523,15 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-15, 2026-03-16, 2026-03-24</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-24</t>
-        </is>
-      </c>
+          <t>2026-03-05, 2026-03-15, 2026-03-21, 2026-03-30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -549,7 +545,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-03-07, 2026-03-15, 2026-03-21, 2026-03-30</t>
+          <t>2026-03-07, 2026-03-15, 2026-03-16, 2026-03-21, 2026-03-31</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
@@ -583,12 +579,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-10, 2026-03-17</t>
+          <t>2026-03-06, 2026-03-11, 2026-03-18</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-10, 2026-03-17</t>
+          <t>2026-03-11, 2026-03-18</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -612,16 +608,12 @@
           <t>2026-03-06, 2026-03-13</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2026-03-06, 2026-03-13</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -673,19 +665,19 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-10, 2026-03-17, 2026-03-25</t>
+          <t>2026-03-07, 2026-03-12, 2026-03-19, 2026-03-25</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-25</t>
+          <t>2026-03-12, 2026-03-19, 2026-03-25</t>
         </is>
       </c>
       <c r="M4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="5">
@@ -711,19 +703,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-03-17, 2026-03-24</t>
+          <t>2026-03-03, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-03-17, 2026-03-24</t>
+          <t>2026-03-03, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
